--- a/data/trans_orig/P1407-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1407-Provincia-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de estreñimiento crónico en 2012</t>
+          <t>Población con diagnóstico de estreñimiento crónico en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -736,7 +736,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8449</t>
+          <t>6950</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3944</t>
+          <t>3961</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17647</t>
+          <t>16660</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5713</t>
+          <t>5077</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18566</t>
+          <t>19229</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>286289</t>
+          <t>287788</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>269598</t>
+          <t>270585</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>283301</t>
+          <t>283284</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>563417</t>
+          <t>562754</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>576270</t>
+          <t>576906</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7078</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6294</t>
+          <t>6224</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19289</t>
+          <t>20420</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7428</t>
+          <t>7746</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22578</t>
+          <t>22149</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>498449</t>
+          <t>498327</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>504476</t>
+          <t>503345</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>517471</t>
+          <t>517541</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1006714</t>
+          <t>1007143</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1021864</t>
+          <t>1021546</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5032</t>
+          <t>4973</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,47 +1452,47 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>992</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2058</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>992</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>4937</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>319014</t>
+          <t>319073</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>338962</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>341020</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>660121</t>
+          <t>660129</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2081</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9990</t>
+          <t>10011</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26538</t>
+          <t>26083</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10330</t>
+          <t>10156</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26895</t>
+          <t>26929</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>371901</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>373982</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>362413</t>
+          <t>362868</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>378961</t>
+          <t>378940</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>736038</t>
+          <t>736004</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>752603</t>
+          <t>752777</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,67%</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6205</t>
+          <t>7158</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4270</t>
+          <t>5126</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16858</t>
+          <t>18311</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5186</t>
+          <t>5310</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18413</t>
+          <t>19170</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>206413</t>
+          <t>205460</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>202733</t>
+          <t>201280</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>215321</t>
+          <t>214465</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>413796</t>
+          <t>413039</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>427023</t>
+          <t>426899</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,77%</t>
         </is>
       </c>
     </row>
@@ -2446,97 +2446,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>4906</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>976</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>5263</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>4894</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>4950</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>271974</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>273981</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>272833</t>
+          <t>273190</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>547127</t>
+          <t>547183</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7253</t>
+          <t>6605</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6269</t>
+          <t>5350</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22084</t>
+          <t>21741</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8134</t>
+          <t>8061</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>25493</t>
+          <t>24557</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>655535</t>
+          <t>656183</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>671769</t>
+          <t>672112</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>687584</t>
+          <t>688503</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1331148</t>
+          <t>1332084</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1348507</t>
+          <t>1348580</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6449</t>
+          <t>7574</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5425</t>
+          <t>6153</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>20834</t>
+          <t>20208</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7274</t>
+          <t>7314</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>23574</t>
+          <t>23362</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>772649</t>
+          <t>771524</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>800561</t>
+          <t>801187</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>815970</t>
+          <t>815242</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1576919</t>
+          <t>1577131</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1593219</t>
+          <t>1593179</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -3475,12 +3475,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5158</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>19472</t>
+          <t>18255</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>54651</t>
+          <t>55118</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>88574</t>
+          <t>89920</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3525,12 +3525,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>65051</t>
+          <t>65148</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>101985</t>
+          <t>101316</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -3588,12 +3588,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3407307</t>
+          <t>3408524</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3421621</t>
+          <t>3421699</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3465342</t>
+          <t>3463996</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3499265</t>
+          <t>3498798</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6878709</t>
+          <t>6879378</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6915643</t>
+          <t>6915546</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de estreñimiento crónico en 2016</t>
+          <t>Población con diagnóstico de estreñimiento crónico en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7420</t>
+          <t>6164</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6516</t>
+          <t>6070</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20708</t>
+          <t>21293</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7212</t>
+          <t>7872</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23221</t>
+          <t>24352</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>286341</t>
+          <t>287597</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>267995</t>
+          <t>267410</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>282187</t>
+          <t>282633</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>559243</t>
+          <t>558112</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>575252</t>
+          <t>574592</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>863</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7931</t>
+          <t>8351</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2071</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>862</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7518</t>
+          <t>7764</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>494644</t>
+          <t>494224</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>501721</t>
+          <t>501712</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>521013</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>523084</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1018141</t>
+          <t>1017895</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1025659</t>
+          <t>1024797</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,92%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>924</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10613</t>
+          <t>10751</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>906</t>
+          <t>901</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8670</t>
+          <t>9175</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2280</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14353</t>
+          <t>13489</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>307952</t>
+          <t>307814</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>317639</t>
+          <t>317641</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>327639</t>
+          <t>327134</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>335403</t>
+          <t>335408</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>640521</t>
+          <t>641385</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>651988</t>
+          <t>652594</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,65%</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4546</t>
+          <t>4536</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3138</t>
+          <t>3243</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15678</t>
+          <t>16183</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3932</t>
+          <t>3952</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17593</t>
+          <t>17038</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>365418</t>
+          <t>365428</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>371605</t>
+          <t>371100</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>384145</t>
+          <t>384040</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>739654</t>
+          <t>740209</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>753315</t>
+          <t>753295</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4531</t>
+          <t>6283</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7184</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>893</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7945</t>
+          <t>7973</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>206690</t>
+          <t>204938</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>211403</t>
+          <t>211432</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>421863</t>
+          <t>421835</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>428918</t>
+          <t>428915</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>808</t>
+          <t>804</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8208</t>
+          <t>8438</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11379</t>
+          <t>10960</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3545</t>
+          <t>3663</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14953</t>
+          <t>15127</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>254915</t>
+          <t>254685</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>262315</t>
+          <t>262319</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>261736</t>
+          <t>262155</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>271849</t>
+          <t>271869</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>521285</t>
+          <t>521111</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>532693</t>
+          <t>532575</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -6117,7 +6117,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7193</t>
+          <t>6804</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>9339</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27342</t>
+          <t>26873</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11220</t>
+          <t>10707</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>30578</t>
+          <t>31135</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -6225,7 +6225,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>649365</t>
+          <t>649754</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>663952</t>
+          <t>664421</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>681502</t>
+          <t>681955</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1317274</t>
+          <t>1316717</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1336632</t>
+          <t>1337145</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -6460,7 +6460,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6889</t>
+          <t>6877</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6450</t>
+          <t>5987</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21113</t>
+          <t>21522</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7513</t>
+          <t>7460</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>24668</t>
+          <t>24828</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>771694</t>
+          <t>771706</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>805054</t>
+          <t>804645</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>819717</t>
+          <t>820180</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1580082</t>
+          <t>1579922</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1597237</t>
+          <t>1597290</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6653,12 +6653,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -6798,12 +6798,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>9731</t>
+          <t>9616</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>26972</t>
+          <t>25600</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>44793</t>
+          <t>43625</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>77009</t>
+          <t>76735</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6868,12 +6868,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>59773</t>
+          <t>58722</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>96054</t>
+          <t>95206</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -6911,12 +6911,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3367378</t>
+          <t>3368750</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3384619</t>
+          <t>3384734</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3467533</t>
+          <t>3467807</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3499749</t>
+          <t>3500917</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6842838</t>
+          <t>6843686</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6879119</t>
+          <t>6880170</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1407-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1407-Provincia-trans_orig.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6950</t>
+          <t>6884</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3961</t>
+          <t>3874</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16660</t>
+          <t>17215</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5077</t>
+          <t>5737</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19229</t>
+          <t>19536</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>287788</t>
+          <t>287854</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>270585</t>
+          <t>270030</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>283284</t>
+          <t>283371</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>562754</t>
+          <t>562447</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>576906</t>
+          <t>576246</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,01%</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6224</t>
+          <t>6217</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20420</t>
+          <t>19980</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7746</t>
+          <t>7423</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22149</t>
+          <t>22201</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>498327</t>
+          <t>499314</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>503345</t>
+          <t>503785</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>517541</t>
+          <t>517548</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1007143</t>
+          <t>1007091</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1021546</t>
+          <t>1021869</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4973</t>
+          <t>4995</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4937</t>
+          <t>5957</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>319073</t>
+          <t>319051</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>660129</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10011</t>
+          <t>9769</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26083</t>
+          <t>25951</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10156</t>
+          <t>10216</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26929</t>
+          <t>25991</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>362868</t>
+          <t>363000</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>378940</t>
+          <t>379182</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>736004</t>
+          <t>736942</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>752777</t>
+          <t>752717</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,66%</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7158</t>
+          <t>5815</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5126</t>
+          <t>5064</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18311</t>
+          <t>16850</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5310</t>
+          <t>5448</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19170</t>
+          <t>19527</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>205460</t>
+          <t>206803</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>201280</t>
+          <t>202741</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>214465</t>
+          <t>214527</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>413039</t>
+          <t>412682</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>426899</t>
+          <t>426761</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4906</t>
+          <t>4873</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2521,7 +2521,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4894</t>
+          <t>5411</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>273190</t>
+          <t>273223</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>547183</t>
+          <t>546666</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6605</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5350</t>
+          <t>6028</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21741</t>
+          <t>22444</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8061</t>
+          <t>7426</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24557</t>
+          <t>25576</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>656183</t>
+          <t>655798</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>672112</t>
+          <t>671409</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>688503</t>
+          <t>687825</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1332084</t>
+          <t>1331065</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1348580</t>
+          <t>1349215</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7574</t>
+          <t>7637</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6153</t>
+          <t>6170</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>20208</t>
+          <t>21272</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7314</t>
+          <t>7296</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>23362</t>
+          <t>22956</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>771524</t>
+          <t>771461</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>801187</t>
+          <t>800123</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>815242</t>
+          <t>815225</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1577131</t>
+          <t>1577537</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1593179</t>
+          <t>1593197</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5160</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>18255</t>
+          <t>19095</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>55118</t>
+          <t>56005</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>89920</t>
+          <t>94767</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3525,12 +3525,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>65148</t>
+          <t>64896</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>101316</t>
+          <t>102906</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -3588,12 +3588,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3408524</t>
+          <t>3407684</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3421699</t>
+          <t>3421619</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3463996</t>
+          <t>3459149</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3498798</t>
+          <t>3497911</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6879378</t>
+          <t>6877788</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6915546</t>
+          <t>6915798</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6164</t>
+          <t>6235</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6070</t>
+          <t>5946</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21293</t>
+          <t>21481</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7872</t>
+          <t>6648</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24352</t>
+          <t>22443</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>287597</t>
+          <t>287526</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>267410</t>
+          <t>267222</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>282633</t>
+          <t>282757</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>558112</t>
+          <t>560021</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>574592</t>
+          <t>575816</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>858</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8351</t>
+          <t>7607</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7764</t>
+          <t>8655</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>494224</t>
+          <t>494968</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>501712</t>
+          <t>501717</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1017895</t>
+          <t>1017004</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>922</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10751</t>
+          <t>10041</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>916</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9175</t>
+          <t>9165</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2280</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13489</t>
+          <t>14117</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>307814</t>
+          <t>308524</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>317641</t>
+          <t>317643</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>327134</t>
+          <t>327144</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>335408</t>
+          <t>335393</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>641385</t>
+          <t>640757</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>652594</t>
+          <t>652252</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4536</t>
+          <t>4988</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3243</t>
+          <t>3167</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16183</t>
+          <t>17030</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3952</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17038</t>
+          <t>17843</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>365428</t>
+          <t>364976</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>371100</t>
+          <t>370253</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>384040</t>
+          <t>384116</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>740209</t>
+          <t>739404</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>753295</t>
+          <t>753367</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,49%</t>
         </is>
       </c>
     </row>
@@ -5431,7 +5431,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6283</t>
+          <t>5039</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>6450</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>893</t>
+          <t>892</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7973</t>
+          <t>8930</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>204938</t>
+          <t>206182</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>211432</t>
+          <t>212137</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>421835</t>
+          <t>420878</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>428915</t>
+          <t>428916</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>804</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8438</t>
+          <t>8809</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10960</t>
+          <t>11103</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3663</t>
+          <t>3480</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15127</t>
+          <t>15250</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>254685</t>
+          <t>254314</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>262319</t>
+          <t>262105</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>262155</t>
+          <t>262012</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>271869</t>
+          <t>271851</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>521111</t>
+          <t>520988</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>532575</t>
+          <t>532758</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,35%</t>
         </is>
       </c>
     </row>
@@ -6117,7 +6117,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6804</t>
+          <t>6582</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9339</t>
+          <t>9726</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>26873</t>
+          <t>26801</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10707</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>31135</t>
+          <t>29423</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -6225,7 +6225,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>649754</t>
+          <t>649976</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>664421</t>
+          <t>664493</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>681955</t>
+          <t>681568</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1316717</t>
+          <t>1318429</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1337145</t>
+          <t>1337138</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6310,7 +6310,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6877</t>
+          <t>6456</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6475,7 +6475,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5987</t>
+          <t>6920</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21522</t>
+          <t>24583</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7460</t>
+          <t>8404</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>24828</t>
+          <t>24844</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6540,7 +6540,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>771706</t>
+          <t>772127</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>804645</t>
+          <t>801584</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>820180</t>
+          <t>819247</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1579922</t>
+          <t>1579906</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1597290</t>
+          <t>1596346</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6658,7 +6658,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -6798,12 +6798,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>9616</t>
+          <t>9717</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>25600</t>
+          <t>25631</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>43625</t>
+          <t>45510</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>76735</t>
+          <t>78059</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6868,12 +6868,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>58722</t>
+          <t>58051</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>95206</t>
+          <t>95174</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6883,7 +6883,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3368750</t>
+          <t>3368719</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3384734</t>
+          <t>3384633</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3467807</t>
+          <t>3466483</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3500917</t>
+          <t>3499032</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6843686</t>
+          <t>6843718</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6880170</t>
+          <t>6880841</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7001,7 +7001,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,16%</t>
         </is>
       </c>
     </row>
